--- a/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
+++ b/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="219">
   <si>
     <t>N0</t>
     <phoneticPr fontId="36" type="noConversion"/>
@@ -733,18 +733,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>D.C 5%로 구입</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
-    <t>D.C 5%로 구입</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
-    <t>김진겸 사원</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>임제훈 사원</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -935,6 +923,23 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>김진겸 사원</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>D.C 5%로 구입</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>D.C 5%로 구입
+201016~ 모터 HW 대여중</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
@@ -4032,7 +4037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S44"/>
@@ -4058,12 +4063,12 @@
   <sheetData>
     <row r="1" spans="1:19" ht="17.25">
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="14.25" thickBot="1">
       <c r="C2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="50.1" customHeight="1">
@@ -4118,7 +4123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="44" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="4" spans="1:19" s="44" customFormat="1" ht="50.1" customHeight="1">
       <c r="A4" s="36"/>
       <c r="B4" s="37">
         <v>1</v>
@@ -4155,7 +4160,7 @@
       </c>
       <c r="M4" s="43"/>
     </row>
-    <row r="5" spans="1:19" s="46" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="5" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
       <c r="A5" s="36"/>
       <c r="B5" s="37">
         <v>2</v>
@@ -4194,7 +4199,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="46" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="6" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
       <c r="A6" s="36"/>
       <c r="B6" s="37">
         <v>3</v>
@@ -4232,7 +4237,7 @@
       <c r="M6" s="43"/>
       <c r="N6" s="48"/>
     </row>
-    <row r="7" spans="1:19" s="46" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="7" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
       <c r="A7" s="36"/>
       <c r="B7" s="37">
         <v>4</v>
@@ -4272,7 +4277,7 @@
       </c>
       <c r="N7" s="48"/>
     </row>
-    <row r="8" spans="1:19" s="46" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="8" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
       <c r="A8" s="36"/>
       <c r="B8" s="37">
         <v>5</v>
@@ -4310,7 +4315,7 @@
       <c r="M8" s="51"/>
       <c r="N8" s="48"/>
     </row>
-    <row r="9" spans="1:19" s="46" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="9" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
       <c r="A9" s="36"/>
       <c r="B9" s="37">
         <v>6</v>
@@ -4347,7 +4352,7 @@
       </c>
       <c r="M9" s="43"/>
     </row>
-    <row r="10" spans="1:19" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="10" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A10" s="19"/>
       <c r="B10" s="13">
         <v>7</v>
@@ -4382,7 +4387,7 @@
       <c r="L10" s="14"/>
       <c r="M10" s="16"/>
     </row>
-    <row r="11" spans="1:19" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="11" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A11" s="19"/>
       <c r="B11" s="13">
         <v>8</v>
@@ -4413,7 +4418,7 @@
       <c r="L11" s="14"/>
       <c r="M11" s="16"/>
     </row>
-    <row r="12" spans="1:19" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="12" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A12" s="19"/>
       <c r="B12" s="13">
         <v>9</v>
@@ -4444,7 +4449,7 @@
       <c r="L12" s="14"/>
       <c r="M12" s="16"/>
     </row>
-    <row r="13" spans="1:19" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="13" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="13">
         <v>10</v>
@@ -4473,7 +4478,7 @@
       <c r="L13" s="14"/>
       <c r="M13" s="16"/>
     </row>
-    <row r="14" spans="1:19" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="14" spans="1:19" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A14" s="22"/>
       <c r="B14" s="13">
         <v>11</v>
@@ -4506,7 +4511,7 @@
       <c r="L14" s="14"/>
       <c r="M14" s="16"/>
     </row>
-    <row r="15" spans="1:19" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="15" spans="1:19" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A15" s="22"/>
       <c r="B15" s="13">
         <v>12</v>
@@ -4541,7 +4546,7 @@
       <c r="L15" s="14"/>
       <c r="M15" s="16"/>
     </row>
-    <row r="16" spans="1:19" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="16" spans="1:19" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A16" s="22"/>
       <c r="B16" s="13">
         <v>13</v>
@@ -4574,7 +4579,7 @@
       <c r="L16" s="14"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="17" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A17" s="22"/>
       <c r="B17" s="13">
         <v>14</v>
@@ -4607,7 +4612,7 @@
       <c r="L17" s="14"/>
       <c r="M17" s="21"/>
     </row>
-    <row r="18" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="18" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A18" s="22"/>
       <c r="B18" s="13">
         <v>15</v>
@@ -4640,7 +4645,7 @@
       <c r="L18" s="14"/>
       <c r="M18" s="21"/>
     </row>
-    <row r="19" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="19" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A19" s="22"/>
       <c r="B19" s="13">
         <v>16</v>
@@ -4673,7 +4678,7 @@
       <c r="L19" s="14"/>
       <c r="M19" s="16"/>
     </row>
-    <row r="20" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="20" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A20" s="22"/>
       <c r="B20" s="13">
         <v>17</v>
@@ -4708,7 +4713,7 @@
       <c r="L20" s="14"/>
       <c r="M20" s="16"/>
     </row>
-    <row r="21" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="21" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A21" s="22"/>
       <c r="B21" s="13">
         <v>18</v>
@@ -4743,7 +4748,7 @@
       <c r="L21" s="14"/>
       <c r="M21" s="16"/>
     </row>
-    <row r="22" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="22" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A22" s="22"/>
       <c r="B22" s="13">
         <v>19</v>
@@ -4778,7 +4783,7 @@
       <c r="L22" s="14"/>
       <c r="M22" s="16"/>
     </row>
-    <row r="23" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="23" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A23" s="22"/>
       <c r="B23" s="13">
         <v>20</v>
@@ -4813,7 +4818,7 @@
       <c r="L23" s="14"/>
       <c r="M23" s="16"/>
     </row>
-    <row r="24" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="24" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A24" s="22"/>
       <c r="B24" s="13">
         <v>21</v>
@@ -4848,7 +4853,7 @@
       <c r="L24" s="14"/>
       <c r="M24" s="16"/>
     </row>
-    <row r="25" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="25" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A25" s="22"/>
       <c r="B25" s="13">
         <v>22</v>
@@ -4883,7 +4888,7 @@
       <c r="L25" s="14"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="26" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A26" s="22"/>
       <c r="B26" s="13">
         <v>23</v>
@@ -4936,7 +4941,7 @@
         <v>122</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H27" s="14">
         <v>24.03</v>
@@ -4955,7 +4960,7 @@
       </c>
       <c r="M27" s="16"/>
       <c r="P27" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4976,7 +4981,7 @@
         <v>106</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H28" s="14">
         <v>24.03</v>
@@ -4994,10 +4999,10 @@
         <v>139</v>
       </c>
       <c r="M28" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="R28" s="8" t="s">
-        <v>13</v>
+        <v>191</v>
+      </c>
+      <c r="Q28" s="8" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5018,7 +5023,7 @@
         <v>107</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H29" s="14">
         <v>24.03</v>
@@ -5037,7 +5042,7 @@
       </c>
       <c r="M29" s="16"/>
       <c r="P29" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5058,7 +5063,7 @@
         <v>108</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H30" s="14">
         <v>24.03</v>
@@ -5073,10 +5078,10 @@
         <v>142</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M30" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="R30" s="8" t="s">
         <v>13</v>
@@ -5100,7 +5105,7 @@
         <v>145</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H31" s="14">
         <v>24.03</v>
@@ -5112,16 +5117,16 @@
         <v>585000</v>
       </c>
       <c r="K31" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="R31" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="M31" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="R31" s="8" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5142,7 +5147,7 @@
         <v>131</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H32" s="14">
         <v>24.03</v>
@@ -5154,13 +5159,13 @@
         <v>585000</v>
       </c>
       <c r="K32" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="M32" s="21" t="s">
         <v>201</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="M32" s="21" t="s">
-        <v>204</v>
       </c>
       <c r="R32" s="8" t="s">
         <v>13</v>
@@ -5184,7 +5189,7 @@
         <v>144</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H33" s="14">
         <v>24.03</v>
@@ -5199,10 +5204,10 @@
         <v>130</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="M33" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="R33" s="8" t="s">
         <v>13</v>
@@ -5226,7 +5231,7 @@
         <v>109</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H34" s="14">
         <v>24.03</v>
@@ -5244,7 +5249,7 @@
         <v>121</v>
       </c>
       <c r="M34" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="R34" s="8" t="s">
         <v>13</v>
@@ -5268,7 +5273,7 @@
         <v>132</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H35" s="14">
         <v>24.03</v>
@@ -5280,14 +5285,14 @@
         <v>585000</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="L35" s="14" t="s">
         <v>138</v>
       </c>
       <c r="M35" s="16"/>
       <c r="P35" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5305,10 +5310,10 @@
         <v>100</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H36" s="14">
         <v>24.03</v>
@@ -5320,19 +5325,19 @@
         <v>585000</v>
       </c>
       <c r="K36" s="14" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="M36" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="R36" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="37" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A37" s="22"/>
       <c r="B37" s="13">
         <v>34</v>
@@ -5367,7 +5372,7 @@
       <c r="L37" s="14"/>
       <c r="M37" s="16"/>
     </row>
-    <row r="38" spans="1:18" s="8" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="38" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A38" s="22"/>
       <c r="B38" s="13">
         <v>35</v>
@@ -5397,14 +5402,14 @@
         <v>9878000</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L38" s="14"/>
-      <c r="M38" s="16" t="s">
-        <v>166</v>
+      <c r="M38" s="21" t="s">
+        <v>217</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="39" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A39" s="19"/>
       <c r="B39" s="13">
         <v>36</v>
@@ -5422,7 +5427,7 @@
         <v>159</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H39" s="14">
         <v>24.12</v>
@@ -5434,14 +5439,14 @@
         <v>9878000</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="L39" s="14"/>
       <c r="M39" s="16" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="40" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A40" s="19"/>
       <c r="B40" s="13">
         <v>37</v>
@@ -5456,10 +5461,10 @@
         <v>157</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H40" s="52">
         <v>24.12</v>
@@ -5471,14 +5476,14 @@
         <v>9878000</v>
       </c>
       <c r="K40" s="24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L40" s="14"/>
       <c r="M40" s="25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="41" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A41" s="19"/>
       <c r="B41" s="13">
         <v>38</v>
@@ -5493,10 +5498,10 @@
         <v>19</v>
       </c>
       <c r="F41" s="24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H41" s="53">
         <v>24.12</v>
@@ -5508,12 +5513,12 @@
         <v>23335000</v>
       </c>
       <c r="K41" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L41" s="24"/>
       <c r="M41" s="25"/>
     </row>
-    <row r="42" spans="1:18" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="42" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A42" s="19"/>
       <c r="B42" s="13">
         <v>39</v>
@@ -5548,86 +5553,80 @@
       <c r="L42" s="24"/>
       <c r="M42" s="25"/>
     </row>
-    <row r="43" spans="1:18" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1">
+    <row r="43" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A43" s="19"/>
       <c r="B43" s="13">
         <v>40</v>
       </c>
       <c r="C43" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="G43" s="24" t="s">
         <v>179</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="G43" s="24" t="s">
-        <v>182</v>
       </c>
       <c r="H43" s="53">
         <v>25.04</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J43" s="30">
         <v>9960000</v>
       </c>
       <c r="K43" s="24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="L43" s="24"/>
       <c r="M43" s="25"/>
     </row>
-    <row r="44" spans="1:18" s="2" customFormat="1" ht="50.1" hidden="1" customHeight="1" thickBot="1">
+    <row r="44" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1" thickBot="1">
       <c r="A44" s="19"/>
       <c r="B44" s="27">
         <v>41</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E44" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="G44" s="28" t="s">
         <v>187</v>
-      </c>
-      <c r="F44" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>190</v>
       </c>
       <c r="H44" s="54">
         <v>25.08</v>
       </c>
       <c r="I44" s="28" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J44" s="32">
         <v>29260000</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L44" s="28" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="M44" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:M44">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Renesas E2 Emulator"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B3:M44"/>
   <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
+++ b/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
@@ -19,7 +19,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="_5____S" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EV HEATER SW'!$B$3:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EV HEATER SW'!$B$3:$M$54</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
     <definedName name="¤A¤A">#REF!</definedName>
     <definedName name="¤μ¤μ">#REF!</definedName>
@@ -29,7 +29,7 @@
     <definedName name="DD">#REF!</definedName>
     <definedName name="EE">#REF!</definedName>
     <definedName name="N">[1]TOTAL!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'EV HEATER SW'!$A$1:$S$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'EV HEATER SW'!$A$1:$Q$55</definedName>
     <definedName name="Print_Area_MI">#REF!</definedName>
     <definedName name="SKFK">#REF!</definedName>
     <definedName name="W">#REF!</definedName>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="230">
   <si>
     <t>N0</t>
     <phoneticPr fontId="36" type="noConversion"/>
@@ -789,10 +789,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>김진겸 사원</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>MXO44 PRO Oscilloscope</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -878,10 +874,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>Last Rev. 25.09.29</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>AS20241211000001_7</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -940,6 +932,58 @@
   </si>
   <si>
     <t>O</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>EV Heater SW 1</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026928D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026927D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026926D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026930D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026925D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026921D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026924D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026922D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026929D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>4KS026923D</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영 수석</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>Last Rev. 25.10.22</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
@@ -1290,7 +1334,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1437,14 +1481,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="25">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1702,30 +1740,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -2917,7 +2931,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2999,89 +3013,50 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="253" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="46" fillId="0" borderId="21" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="23" xfId="253" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="24" xfId="253" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="46" fillId="0" borderId="23" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="46" fillId="0" borderId="3" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="46" fillId="29" borderId="3" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="46" fillId="29" borderId="3" xfId="142" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="23" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="418">
@@ -4040,7 +4015,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
@@ -4053,25 +4028,23 @@
     <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.77734375" customWidth="1"/>
     <col min="13" max="13" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.109375" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="8.88671875" customWidth="1"/>
+    <col min="14" max="18" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="17.25">
+    <row r="1" spans="1:17" ht="17.25">
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="14.25" thickBot="1">
+    <row r="2" spans="1:17" ht="14.25" thickBot="1">
       <c r="C2" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="50.1" customHeight="1">
+    <row r="3" spans="1:17" ht="50.1" customHeight="1">
       <c r="A3" s="23"/>
       <c r="B3" s="9" t="s">
         <v>0</v>
@@ -4109,824 +4082,846 @@
       <c r="M3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="33"/>
-      <c r="P3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="44" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37">
+    <row r="4" spans="1:17" s="41" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A4" s="19"/>
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="M4" s="43"/>
+      <c r="C4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="18">
+        <v>831</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="14"/>
+      <c r="M4" s="16"/>
     </row>
-    <row r="5" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A5" s="36"/>
-      <c r="B5" s="37">
+    <row r="5" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A5" s="19"/>
+      <c r="B5" s="13">
         <v>2</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5" s="39" t="s">
+      <c r="C5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="H5" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="L5" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="M5" s="45" t="s">
-        <v>88</v>
-      </c>
+      <c r="H5" s="14">
+        <v>23.05</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="28">
+        <v>792000</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="14"/>
+      <c r="M5" s="16"/>
     </row>
-    <row r="6" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="37">
+    <row r="6" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A6" s="19"/>
+      <c r="B6" s="13">
         <v>3</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="38">
-        <v>23.03</v>
-      </c>
-      <c r="I6" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="42">
-        <v>9591000</v>
-      </c>
-      <c r="K6" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="L6" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="M6" s="43"/>
-      <c r="N6" s="48"/>
+      <c r="C6" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="14">
+        <v>23.05</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="28">
+        <v>792000</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="14"/>
+      <c r="M6" s="16"/>
     </row>
-    <row r="7" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A7" s="36"/>
-      <c r="B7" s="37">
+    <row r="7" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A7" s="19"/>
+      <c r="B7" s="13">
         <v>4</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I7" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="J7" s="42">
-        <v>9591001</v>
-      </c>
-      <c r="K7" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="N7" s="48"/>
+      <c r="C7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="14">
+        <v>23.05</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="28">
+        <v>792000</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="14"/>
+      <c r="M7" s="16"/>
     </row>
-    <row r="8" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A8" s="36"/>
-      <c r="B8" s="37">
+    <row r="8" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A8" s="19"/>
+      <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" s="39" t="s">
+      <c r="C8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="H8" s="38">
-        <v>23.06</v>
-      </c>
-      <c r="I8" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="49">
-        <v>11569000</v>
-      </c>
-      <c r="K8" s="38" t="s">
+      <c r="H8" s="14">
+        <v>23.05</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="28">
+        <v>792000</v>
+      </c>
+      <c r="K8" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="M8" s="51"/>
-      <c r="N8" s="48"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="16"/>
     </row>
-    <row r="9" spans="1:19" s="46" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="37">
+    <row r="9" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="13">
         <v>6</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="38">
-        <v>23.06</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="42">
-        <v>22113000</v>
-      </c>
-      <c r="K9" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="M9" s="43"/>
+      <c r="C9" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="H9" s="14">
+        <v>24.03</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="28">
+        <v>585000</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>200</v>
+      </c>
     </row>
-    <row r="10" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
+    <row r="10" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A10" s="19"/>
       <c r="B10" s="13">
         <v>7</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>35</v>
+      <c r="C10" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H10" s="14">
-        <v>19.12</v>
+        <v>23.06</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="31">
-        <v>11000000</v>
+        <v>20</v>
+      </c>
+      <c r="J10" s="27">
+        <v>22113000</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="14"/>
+      <c r="L10" s="14" t="s">
+        <v>148</v>
+      </c>
       <c r="M10" s="16"/>
     </row>
-    <row r="11" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
+    <row r="11" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A11" s="19"/>
       <c r="B11" s="13">
         <v>8</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>54</v>
+        <v>82</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>80</v>
+        <v>59</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="14">
+        <v>23.03</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="30"/>
+        <v>61</v>
+      </c>
+      <c r="J11" s="27">
+        <v>9591000</v>
+      </c>
       <c r="K11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>148</v>
+      </c>
       <c r="M11" s="16"/>
     </row>
-    <row r="12" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
+    <row r="12" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A12" s="19"/>
       <c r="B12" s="13">
         <v>9</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="18"/>
+        <v>157</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="G12" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>80</v>
+        <v>163</v>
+      </c>
+      <c r="H12" s="14">
+        <v>24.12</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="J12" s="31"/>
-      <c r="K12" s="14" t="s">
-        <v>50</v>
+        <v>164</v>
+      </c>
+      <c r="J12" s="27">
+        <v>9878000</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>167</v>
       </c>
       <c r="L12" s="14"/>
-      <c r="M12" s="16"/>
+      <c r="M12" s="21" t="s">
+        <v>215</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" s="2" customFormat="1" ht="50.1" customHeight="1">
+    <row r="13" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="13">
         <v>10</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+        <v>156</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>159</v>
+      </c>
       <c r="G13" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>80</v>
+        <v>170</v>
+      </c>
+      <c r="H13" s="14">
+        <v>24.12</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="J13" s="30"/>
-      <c r="K13" s="14" t="s">
-        <v>50</v>
+        <v>164</v>
+      </c>
+      <c r="J13" s="27">
+        <v>9878000</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>213</v>
       </c>
       <c r="L13" s="14"/>
-      <c r="M13" s="16"/>
+      <c r="M13" s="16" t="s">
+        <v>214</v>
+      </c>
     </row>
-    <row r="14" spans="1:19" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="14" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A14" s="22"/>
       <c r="B14" s="13">
         <v>11</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>42</v>
+      <c r="C14" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="18">
-        <v>831</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" s="31"/>
-      <c r="K14" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" s="14"/>
-      <c r="M14" s="16"/>
+        <v>156</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="33">
+        <v>24.12</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="J14" s="27">
+        <v>23335000</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="L14" s="24"/>
+      <c r="M14" s="25"/>
     </row>
-    <row r="15" spans="1:19" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="15" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A15" s="22"/>
       <c r="B15" s="13">
         <v>12</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>24</v>
+      <c r="C15" s="14" t="s">
+        <v>84</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>27</v>
+        <v>74</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>151</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="14">
-        <v>19.02</v>
+        <v>75</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" s="31">
-        <v>11200000</v>
+        <v>76</v>
+      </c>
+      <c r="J15" s="27">
+        <v>9591001</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" s="14"/>
-      <c r="M15" s="16"/>
+        <v>77</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="16" spans="1:19" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="16" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A16" s="22"/>
       <c r="B16" s="13">
         <v>13</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J16" s="30"/>
-      <c r="K16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="21"/>
+      <c r="C16" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="H16" s="33">
+        <v>24.12</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="J16" s="27">
+        <v>23335000</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" s="24"/>
+      <c r="M16" s="25"/>
     </row>
-    <row r="17" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="17" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A17" s="22"/>
       <c r="B17" s="13">
         <v>14</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>67</v>
+        <v>154</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>156</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>80</v>
+        <v>169</v>
+      </c>
+      <c r="H17" s="32">
+        <v>24.12</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="14" t="s">
-        <v>62</v>
+        <v>165</v>
+      </c>
+      <c r="J17" s="27">
+        <v>9878000</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="L17" s="14"/>
-      <c r="M17" s="21"/>
+      <c r="M17" s="25" t="s">
+        <v>166</v>
+      </c>
     </row>
-    <row r="18" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="18" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A18" s="22"/>
       <c r="B18" s="13">
         <v>15</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>67</v>
+        <v>79</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>97</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="J18" s="30"/>
+        <v>61</v>
+      </c>
+      <c r="J18" s="27" t="s">
+        <v>81</v>
+      </c>
       <c r="K18" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="21"/>
+        <v>62</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M18" s="16"/>
     </row>
-    <row r="19" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="19" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A19" s="22"/>
       <c r="B19" s="13">
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>96</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J19" s="31"/>
+        <v>61</v>
+      </c>
+      <c r="J19" s="27" t="s">
+        <v>81</v>
+      </c>
       <c r="K19" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" s="14"/>
-      <c r="M19" s="16"/>
+        <v>64</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="20" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="20" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A20" s="22"/>
       <c r="B20" s="13">
         <v>17</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>38</v>
+        <v>101</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="15" t="s">
         <v>96</v>
       </c>
       <c r="H20" s="14">
-        <v>23.05</v>
+        <v>23.06</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J20" s="31">
-        <v>792000</v>
+        <v>104</v>
+      </c>
+      <c r="J20" s="28">
+        <v>11569000</v>
       </c>
       <c r="K20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="16"/>
+      <c r="L20" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="M20" s="40"/>
     </row>
-    <row r="21" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="21" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A21" s="22"/>
       <c r="B21" s="13">
         <v>18</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>38</v>
+        <v>94</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="H21" s="14">
-        <v>23.05</v>
+      <c r="H21" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J21" s="31">
-        <v>792000</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="J21" s="28"/>
       <c r="K21" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="16"/>
     </row>
-    <row r="22" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="22" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A22" s="22"/>
       <c r="B22" s="13">
         <v>19</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H22" s="14">
-        <v>23.05</v>
+        <v>67</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="31">
-        <v>792000</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="J22" s="27"/>
       <c r="K22" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L22" s="14"/>
-      <c r="M22" s="16"/>
+      <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="23" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A23" s="22"/>
       <c r="B23" s="13">
         <v>20</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H23" s="14">
-        <v>23.05</v>
+        <v>67</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="31">
-        <v>792000</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="J23" s="27"/>
       <c r="K23" s="14" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="L23" s="14"/>
-      <c r="M23" s="16"/>
+      <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="24" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A24" s="22"/>
       <c r="B24" s="13">
         <v>21</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>90</v>
+        <v>66</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="H24" s="14">
-        <v>23.05</v>
+        <v>68</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="J24" s="34" t="s">
-        <v>92</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="J24" s="27"/>
       <c r="K24" s="14" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="L24" s="14"/>
-      <c r="M24" s="16"/>
+      <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="25" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A25" s="22"/>
       <c r="B25" s="13">
         <v>22</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="H25" s="14">
-        <v>23.05</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="J25" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="21"/>
+      <c r="C25" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="33">
+        <v>25.08</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" s="27">
+        <v>29260000</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="M25" s="25"/>
     </row>
-    <row r="26" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="26" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A26" s="22"/>
       <c r="B26" s="13">
         <v>23</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="H26" s="14" t="s">
-        <v>80</v>
+      <c r="H26" s="14">
+        <v>23.05</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="30" t="s">
-        <v>14</v>
+        <v>114</v>
+      </c>
+      <c r="J26" s="31" t="s">
+        <v>92</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="L26" s="14"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="27" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A27" s="22"/>
       <c r="B27" s="13">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>124</v>
@@ -4941,7 +4936,7 @@
         <v>122</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H27" s="14">
         <v>24.03</v>
@@ -4949,7 +4944,7 @@
       <c r="I27" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="27">
         <v>585000</v>
       </c>
       <c r="K27" s="15" t="s">
@@ -4959,14 +4954,14 @@
         <v>140</v>
       </c>
       <c r="M27" s="16"/>
-      <c r="P27" s="8" t="s">
-        <v>196</v>
+      <c r="N27" s="8" t="s">
+        <v>195</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="28" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A28" s="22"/>
       <c r="B28" s="13">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>98</v>
@@ -4981,7 +4976,7 @@
         <v>106</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H28" s="14">
         <v>24.03</v>
@@ -4989,7 +4984,7 @@
       <c r="I28" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="28">
         <v>585000</v>
       </c>
       <c r="K28" s="14" t="s">
@@ -4999,16 +4994,16 @@
         <v>139</v>
       </c>
       <c r="M28" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q28" s="8" t="s">
-        <v>218</v>
+        <v>190</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="29" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A29" s="22"/>
       <c r="B29" s="13">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>98</v>
@@ -5023,7 +5018,7 @@
         <v>107</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H29" s="14">
         <v>24.03</v>
@@ -5031,7 +5026,7 @@
       <c r="I29" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="28">
         <v>585000</v>
       </c>
       <c r="K29" s="14" t="s">
@@ -5041,14 +5036,14 @@
         <v>141</v>
       </c>
       <c r="M29" s="16"/>
-      <c r="P29" s="8" t="s">
-        <v>195</v>
+      <c r="N29" s="8" t="s">
+        <v>194</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="30" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A30" s="22"/>
       <c r="B30" s="13">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>98</v>
@@ -5063,7 +5058,7 @@
         <v>108</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H30" s="14">
         <v>24.03</v>
@@ -5071,26 +5066,26 @@
       <c r="I30" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="28">
         <v>585000</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>142</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M30" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="R30" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="31" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A31" s="22"/>
       <c r="B31" s="13">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>98</v>
@@ -5105,7 +5100,7 @@
         <v>145</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H31" s="14">
         <v>24.03</v>
@@ -5113,26 +5108,26 @@
       <c r="I31" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="28">
         <v>585000</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M31" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="R31" s="8" t="s">
         <v>200</v>
       </c>
+      <c r="P31" s="8" t="s">
+        <v>199</v>
+      </c>
     </row>
-    <row r="32" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="32" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A32" s="22"/>
       <c r="B32" s="13">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>98</v>
@@ -5147,7 +5142,7 @@
         <v>131</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H32" s="14">
         <v>24.03</v>
@@ -5155,110 +5150,108 @@
       <c r="I32" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="28">
         <v>585000</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M32" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="R32" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="33" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A33" s="22"/>
       <c r="B33" s="13">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>128</v>
+        <v>98</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>144</v>
+        <v>100</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H33" s="14">
         <v>24.03</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="J33" s="30">
+        <v>105</v>
+      </c>
+      <c r="J33" s="28">
         <v>585000</v>
       </c>
-      <c r="K33" s="15" t="s">
-        <v>130</v>
+      <c r="K33" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="M33" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="R33" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="M33" s="16"/>
+      <c r="P33" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="34" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A34" s="22"/>
       <c r="B34" s="13">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>99</v>
+        <v>127</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>109</v>
+        <v>129</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H34" s="14">
         <v>24.03</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="J34" s="31">
+        <v>126</v>
+      </c>
+      <c r="J34" s="27">
         <v>585000</v>
       </c>
-      <c r="K34" s="14" t="s">
-        <v>137</v>
+      <c r="K34" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="M34" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="R34" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="P34" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="35" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A35" s="22"/>
       <c r="B35" s="13">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>98</v>
@@ -5270,10 +5263,10 @@
         <v>100</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H35" s="14">
         <v>24.03</v>
@@ -5281,24 +5274,26 @@
       <c r="I35" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J35" s="31">
+      <c r="J35" s="28">
         <v>585000</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="L35" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="M35" s="16"/>
-      <c r="P35" s="8" t="s">
-        <v>196</v>
+        <v>121</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="36" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A36" s="22"/>
       <c r="B36" s="13">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>98</v>
@@ -5310,323 +5305,651 @@
         <v>100</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>210</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="G36" s="15"/>
       <c r="H36" s="14">
-        <v>24.03</v>
+        <v>25.09</v>
       </c>
       <c r="I36" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="J36" s="31">
-        <v>585000</v>
-      </c>
-      <c r="K36" s="14" t="s">
-        <v>199</v>
+      <c r="J36" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>217</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="M36" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="R36" s="8" t="s">
-        <v>194</v>
+        <v>140</v>
+      </c>
+      <c r="M36" s="21"/>
+      <c r="P36" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="37" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A37" s="22"/>
       <c r="B37" s="13">
         <v>34</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>133</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="G37" s="15"/>
       <c r="H37" s="14">
-        <v>23.01</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="J37" s="31">
-        <v>708058</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L37" s="14"/>
-      <c r="M37" s="16"/>
+        <v>25.09</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M37" s="21"/>
     </row>
-    <row r="38" spans="1:18" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="38" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A38" s="22"/>
       <c r="B38" s="13">
         <v>35</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>163</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="G38" s="15"/>
       <c r="H38" s="14">
-        <v>24.12</v>
+        <v>25.09</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="J38" s="30">
-        <v>9878000</v>
+        <v>105</v>
+      </c>
+      <c r="J38" s="27">
+        <v>570000</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="L38" s="14"/>
-      <c r="M38" s="21" t="s">
         <v>217</v>
       </c>
+      <c r="L38" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M38" s="21"/>
     </row>
-    <row r="39" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A39" s="19"/>
+    <row r="39" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A39" s="22"/>
       <c r="B39" s="13">
         <v>36</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>156</v>
+        <v>127</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>170</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="G39" s="15"/>
       <c r="H39" s="14">
-        <v>24.12</v>
+        <v>25.09</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="J39" s="30">
-        <v>9878000</v>
+        <v>126</v>
+      </c>
+      <c r="J39" s="27">
+        <v>570000</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="L39" s="14"/>
-      <c r="M39" s="16" t="s">
-        <v>216</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M39" s="21"/>
     </row>
-    <row r="40" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A40" s="19"/>
+    <row r="40" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A40" s="22"/>
       <c r="B40" s="13">
         <v>37</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40" s="52">
-        <v>24.12</v>
+        <v>100</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" s="15"/>
+      <c r="H40" s="14">
+        <v>25.09</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="J40" s="30">
-        <v>9878000</v>
-      </c>
-      <c r="K40" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="L40" s="14"/>
-      <c r="M40" s="25" t="s">
-        <v>166</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="J40" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M40" s="21"/>
     </row>
-    <row r="41" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A41" s="19"/>
+    <row r="41" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A41" s="22"/>
       <c r="B41" s="13">
         <v>38</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>155</v>
+      <c r="C41" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E41" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="G41" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="H41" s="53">
-        <v>24.12</v>
-      </c>
-      <c r="I41" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="J41" s="30">
-        <v>23335000</v>
-      </c>
-      <c r="K41" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="L41" s="24"/>
-      <c r="M41" s="25"/>
+        <v>99</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="G41" s="15"/>
+      <c r="H41" s="14">
+        <v>25.09</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J41" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M41" s="16"/>
     </row>
-    <row r="42" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A42" s="19"/>
+    <row r="42" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A42" s="22"/>
       <c r="B42" s="13">
         <v>39</v>
       </c>
-      <c r="C42" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F42" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="H42" s="53">
-        <v>24.12</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="J42" s="30">
-        <v>23335000</v>
-      </c>
-      <c r="K42" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="L42" s="24"/>
-      <c r="M42" s="25"/>
+      <c r="C42" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="G42" s="15"/>
+      <c r="H42" s="14">
+        <v>25.09</v>
+      </c>
+      <c r="I42" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J42" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M42" s="21"/>
     </row>
-    <row r="43" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A43" s="19"/>
+    <row r="43" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A43" s="22"/>
       <c r="B43" s="13">
         <v>40</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="G43" s="15"/>
+      <c r="H43" s="14">
+        <v>25.09</v>
+      </c>
+      <c r="I43" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="J43" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L43" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M43" s="16"/>
+    </row>
+    <row r="44" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A44" s="22"/>
+      <c r="B44" s="13">
+        <v>41</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="G44" s="15"/>
+      <c r="H44" s="14">
+        <v>25.09</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J44" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M44" s="16"/>
+    </row>
+    <row r="45" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A45" s="22"/>
+      <c r="B45" s="13">
+        <v>42</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G45" s="15"/>
+      <c r="H45" s="14">
+        <v>25.09</v>
+      </c>
+      <c r="I45" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J45" s="27">
+        <v>570000</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="M45" s="21"/>
+    </row>
+    <row r="46" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A46" s="22"/>
+      <c r="B46" s="13">
+        <v>43</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="L46" s="14"/>
+      <c r="M46" s="21"/>
+    </row>
+    <row r="47" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A47" s="22"/>
+      <c r="B47" s="13">
+        <v>44</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H47" s="14">
+        <v>23.05</v>
+      </c>
+      <c r="I47" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J47" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L47" s="14"/>
+      <c r="M47" s="16"/>
+    </row>
+    <row r="48" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A48" s="22"/>
+      <c r="B48" s="13">
+        <v>45</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H48" s="14">
+        <v>19.02</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J48" s="28">
+        <v>11200000</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="14"/>
+      <c r="M48" s="16"/>
+    </row>
+    <row r="49" spans="1:13" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A49" s="19"/>
+      <c r="B49" s="13">
+        <v>46</v>
+      </c>
+      <c r="C49" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D49" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="E49" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="F43" s="24" t="s">
+      <c r="F49" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="G43" s="24" t="s">
+      <c r="G49" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="H43" s="53">
+      <c r="H49" s="33">
         <v>25.04</v>
       </c>
-      <c r="I43" s="24" t="s">
+      <c r="I49" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="J43" s="30">
+      <c r="J49" s="27">
         <v>9960000</v>
       </c>
-      <c r="K43" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="L43" s="24"/>
-      <c r="M43" s="25"/>
+      <c r="K49" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="L49" s="24"/>
+      <c r="M49" s="25"/>
     </row>
-    <row r="44" spans="1:18" s="2" customFormat="1" ht="50.1" customHeight="1" thickBot="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="27">
+    <row r="50" spans="1:13" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A50" s="19"/>
+      <c r="B50" s="13">
+        <v>47</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="14">
+        <v>19.12</v>
+      </c>
+      <c r="I50" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="28">
+        <v>11000000</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L50" s="14"/>
+      <c r="M50" s="16"/>
+    </row>
+    <row r="51" spans="1:13" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A51" s="19"/>
+      <c r="B51" s="13">
+        <v>48</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="D44" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="F44" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="H44" s="54">
-        <v>25.08</v>
-      </c>
-      <c r="I44" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="J44" s="32">
-        <v>29260000</v>
-      </c>
-      <c r="K44" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="L44" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="M44" s="29"/>
+      <c r="F51" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H51" s="14">
+        <v>23.01</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="J51" s="28">
+        <v>708058</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="L51" s="14"/>
+      <c r="M51" s="16"/>
+    </row>
+    <row r="52" spans="1:13" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A52" s="19"/>
+      <c r="B52" s="13">
+        <v>49</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="27"/>
+      <c r="K52" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L52" s="14"/>
+      <c r="M52" s="16"/>
+    </row>
+    <row r="53" spans="1:13" s="2" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A53" s="19"/>
+      <c r="B53" s="13">
+        <v>50</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="18"/>
+      <c r="G53" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="J53" s="28"/>
+      <c r="K53" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="L53" s="14"/>
+      <c r="M53" s="16"/>
+    </row>
+    <row r="54" spans="1:13" s="2" customFormat="1" ht="50.1" customHeight="1" thickBot="1">
+      <c r="A54" s="19"/>
+      <c r="B54" s="13">
+        <v>51</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="H54" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="I54" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="J54" s="29"/>
+      <c r="K54" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="L54" s="34"/>
+      <c r="M54" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:M44"/>
+  <autoFilter ref="B3:M54">
+    <sortState ref="B4:M54">
+      <sortCondition ref="F4:F54"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="36" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="59" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
+++ b/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="232">
   <si>
     <t>N0</t>
     <phoneticPr fontId="36" type="noConversion"/>
@@ -983,7 +983,15 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>Last Rev. 25.10.22</t>
+    <t>김진겸 사원</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>조현진 전임</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>Last Rev. 25.10.27</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
@@ -4041,7 +4049,7 @@
     </row>
     <row r="2" spans="1:17" ht="14.25" thickBot="1">
       <c r="C2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="50.1" customHeight="1">
@@ -5566,7 +5574,7 @@
         <v>570000</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="L43" s="14" t="s">
         <v>140</v>
@@ -5601,7 +5609,7 @@
         <v>570000</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="L44" s="14" t="s">
         <v>140</v>
@@ -5636,7 +5644,7 @@
         <v>570000</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="L45" s="14" t="s">
         <v>140</v>

--- a/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
+++ b/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="243">
   <si>
     <t>N0</t>
     <phoneticPr fontId="36" type="noConversion"/>
@@ -846,10 +846,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>PTC SW</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -991,7 +987,56 @@
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
-    <t>Last Rev. 25.10.27</t>
+    <t>대여 중
+-슬로바키아 법인 보유중-</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_2</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_3</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_4</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_1</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_5</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_6</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_7</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_9</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_10</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20250930000011_8</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>Last Rev. 25.11.05</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
@@ -4044,12 +4089,12 @@
   <sheetData>
     <row r="1" spans="1:17" ht="17.25">
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="14.25" thickBot="1">
       <c r="C2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="50.1" customHeight="1">
@@ -4291,10 +4336,10 @@
         <v>100</v>
       </c>
       <c r="F9" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>207</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>208</v>
       </c>
       <c r="H9" s="14">
         <v>24.03</v>
@@ -4306,13 +4351,13 @@
         <v>585000</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L9" s="14" t="s">
         <v>191</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
@@ -4423,7 +4468,7 @@
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
@@ -4456,11 +4501,11 @@
         <v>9878000</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L13" s="14"/>
       <c r="M13" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4944,7 +4989,7 @@
         <v>122</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H27" s="14">
         <v>24.03</v>
@@ -4963,7 +5008,7 @@
       </c>
       <c r="M27" s="16"/>
       <c r="N27" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4984,7 +5029,7 @@
         <v>106</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H28" s="14">
         <v>24.03</v>
@@ -5005,7 +5050,7 @@
         <v>190</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5026,7 +5071,7 @@
         <v>107</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H29" s="14">
         <v>24.03</v>
@@ -5043,9 +5088,11 @@
       <c r="L29" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="M29" s="16"/>
-      <c r="N29" s="8" t="s">
-        <v>194</v>
+      <c r="M29" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="O29" s="8" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5066,7 +5113,7 @@
         <v>108</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H30" s="14">
         <v>24.03</v>
@@ -5084,7 +5131,7 @@
         <v>192</v>
       </c>
       <c r="M30" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P30" s="8" t="s">
         <v>13</v>
@@ -5108,7 +5155,7 @@
         <v>145</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H31" s="14">
         <v>24.03</v>
@@ -5120,16 +5167,16 @@
         <v>585000</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L31" s="14" t="s">
         <v>191</v>
       </c>
       <c r="M31" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5150,7 +5197,7 @@
         <v>131</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H32" s="14">
         <v>24.03</v>
@@ -5162,13 +5209,13 @@
         <v>585000</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L32" s="14" t="s">
         <v>192</v>
       </c>
       <c r="M32" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P32" s="8" t="s">
         <v>13</v>
@@ -5192,7 +5239,7 @@
         <v>132</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H33" s="14">
         <v>24.03</v>
@@ -5232,7 +5279,7 @@
         <v>144</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H34" s="14">
         <v>24.03</v>
@@ -5250,7 +5297,7 @@
         <v>191</v>
       </c>
       <c r="M34" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P34" s="8" t="s">
         <v>13</v>
@@ -5274,7 +5321,7 @@
         <v>109</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H35" s="14">
         <v>24.03</v>
@@ -5292,10 +5339,10 @@
         <v>121</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5313,9 +5360,11 @@
         <v>100</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="G36" s="15"/>
+        <v>222</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>239</v>
+      </c>
       <c r="H36" s="14">
         <v>25.09</v>
       </c>
@@ -5326,7 +5375,7 @@
         <v>570000</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L36" s="14" t="s">
         <v>140</v>
@@ -5351,9 +5400,11 @@
         <v>100</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="G37" s="15"/>
+        <v>224</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>241</v>
+      </c>
       <c r="H37" s="14">
         <v>25.09</v>
       </c>
@@ -5364,7 +5415,7 @@
         <v>570000</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L37" s="14" t="s">
         <v>140</v>
@@ -5386,9 +5437,11 @@
         <v>100</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="G38" s="15"/>
+        <v>226</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>237</v>
+      </c>
       <c r="H38" s="14">
         <v>25.09</v>
       </c>
@@ -5399,7 +5452,7 @@
         <v>570000</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L38" s="14" t="s">
         <v>140</v>
@@ -5421,9 +5474,11 @@
         <v>129</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="G39" s="15"/>
+        <v>223</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>235</v>
+      </c>
       <c r="H39" s="14">
         <v>25.09</v>
       </c>
@@ -5434,7 +5489,7 @@
         <v>570000</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L39" s="14" t="s">
         <v>140</v>
@@ -5456,9 +5511,11 @@
         <v>100</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="G40" s="15"/>
+        <v>221</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>240</v>
+      </c>
       <c r="H40" s="14">
         <v>25.09</v>
       </c>
@@ -5469,7 +5526,7 @@
         <v>570000</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L40" s="14" t="s">
         <v>140</v>
@@ -5491,9 +5548,11 @@
         <v>100</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="G41" s="15"/>
+        <v>219</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>236</v>
+      </c>
       <c r="H41" s="14">
         <v>25.09</v>
       </c>
@@ -5504,7 +5563,7 @@
         <v>570000</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L41" s="14" t="s">
         <v>140</v>
@@ -5526,9 +5585,11 @@
         <v>100</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="G42" s="15"/>
+        <v>218</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>238</v>
+      </c>
       <c r="H42" s="14">
         <v>25.09</v>
       </c>
@@ -5539,7 +5600,7 @@
         <v>570000</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L42" s="14" t="s">
         <v>140</v>
@@ -5561,9 +5622,11 @@
         <v>110</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="G43" s="15"/>
+        <v>217</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>232</v>
+      </c>
       <c r="H43" s="14">
         <v>25.09</v>
       </c>
@@ -5574,7 +5637,7 @@
         <v>570000</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L43" s="14" t="s">
         <v>140</v>
@@ -5596,9 +5659,11 @@
         <v>100</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="G44" s="15"/>
+        <v>225</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>234</v>
+      </c>
       <c r="H44" s="14">
         <v>25.09</v>
       </c>
@@ -5631,9 +5696,11 @@
         <v>100</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="G45" s="15"/>
+        <v>220</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>233</v>
+      </c>
       <c r="H45" s="14">
         <v>25.09</v>
       </c>
@@ -5644,7 +5711,7 @@
         <v>570000</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L45" s="14" t="s">
         <v>140</v>
@@ -5786,7 +5853,7 @@
         <v>9960000</v>
       </c>
       <c r="K49" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L49" s="24"/>
       <c r="M49" s="25"/>

--- a/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
+++ b/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="239">
   <si>
     <t>N0</t>
     <phoneticPr fontId="36" type="noConversion"/>
@@ -104,10 +104,6 @@
   </si>
   <si>
     <t>유/무</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
-    <t>O</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
@@ -145,14 +141,6 @@
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
-    <t>007114-525699</t>
-    <phoneticPr fontId="41" type="noConversion"/>
-  </si>
-  <si>
-    <t>AS20210520000001</t>
-    <phoneticPr fontId="41" type="noConversion"/>
-  </si>
-  <si>
     <t>Power DC 계열
 Debugger</t>
     <phoneticPr fontId="41" type="noConversion"/>
@@ -369,10 +357,6 @@
   </si>
   <si>
     <t>EV Heater SW</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
-    <t>EV Heater SW</t>
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
@@ -761,10 +745,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>강민구 전임</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>TSMaster UDS Basic / Basic Plus</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -838,14 +818,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
-    <t>O</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>PTC SW</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -858,10 +830,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>고장</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -911,10 +879,6 @@
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
-    <t>김진겸 사원</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
@@ -927,10 +891,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>EV Heater SW 1</t>
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
@@ -983,19 +943,11 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>조현진 전임</t>
-    <phoneticPr fontId="41" type="noConversion"/>
-  </si>
-  <si>
     <t>대여 중
 -슬로바키아 법인 보유중-</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>AS20250930000011_2</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -1037,6 +989,38 @@
   </si>
   <si>
     <t>Last Rev. 25.11.05</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>IJAZ</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>조현진 전임</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>조성연 전임</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>MANJESH</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>AS20210520000001</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>007114-525699</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>김영준 수석</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>2팀 대여 중</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
@@ -4089,12 +4073,12 @@
   <sheetData>
     <row r="1" spans="1:17" ht="17.25">
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="14.25" thickBot="1">
       <c r="C2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="50.1" customHeight="1">
@@ -4136,16 +4120,16 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="41" customFormat="1" ht="50.1" customHeight="1">
@@ -4154,29 +4138,29 @@
         <v>1</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F4" s="18">
         <v>831</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J4" s="28"/>
       <c r="K4" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L4" s="14"/>
       <c r="M4" s="16"/>
@@ -4187,31 +4171,31 @@
         <v>2</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H5" s="14">
         <v>23.05</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J5" s="28">
         <v>792000</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L5" s="14"/>
       <c r="M5" s="16"/>
@@ -4222,31 +4206,31 @@
         <v>3</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H6" s="14">
         <v>23.05</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J6" s="28">
         <v>792000</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L6" s="14"/>
       <c r="M6" s="16"/>
@@ -4257,31 +4241,31 @@
         <v>4</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H7" s="14">
         <v>23.05</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J7" s="28">
         <v>792000</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L7" s="14"/>
       <c r="M7" s="16"/>
@@ -4292,31 +4276,31 @@
         <v>5</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H8" s="14">
         <v>23.05</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J8" s="28">
         <v>792000</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L8" s="14"/>
       <c r="M8" s="16"/>
@@ -4327,37 +4311,37 @@
         <v>6</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H9" s="14">
         <v>24.03</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J9" s="28">
         <v>585000</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="L9" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="M9" s="21" t="s">
         <v>191</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
@@ -4366,34 +4350,34 @@
         <v>7</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>23</v>
+        <v>235</v>
       </c>
       <c r="H10" s="14">
         <v>23.06</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J10" s="27">
         <v>22113000</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M10" s="16"/>
     </row>
@@ -4403,34 +4387,34 @@
         <v>8</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H11" s="14">
         <v>23.03</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J11" s="27">
         <v>9591000</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M11" s="16"/>
     </row>
@@ -4440,35 +4424,35 @@
         <v>9</v>
       </c>
       <c r="C12" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>157</v>
-      </c>
       <c r="F12" s="14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H12" s="14">
         <v>24.12</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J12" s="27">
         <v>9878000</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="21" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
@@ -4477,35 +4461,35 @@
         <v>10</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>157</v>
-      </c>
       <c r="F13" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H13" s="14">
         <v>24.12</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J13" s="27">
         <v>9878000</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="L13" s="14"/>
       <c r="M13" s="16" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4514,31 +4498,31 @@
         <v>11</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H14" s="33">
         <v>24.12</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J14" s="27">
         <v>23335000</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L14" s="24"/>
       <c r="M14" s="25"/>
@@ -4549,37 +4533,37 @@
         <v>12</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J15" s="27">
         <v>9591001</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M15" s="21" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4588,1237 +4572,1209 @@
         <v>13</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E16" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="24" t="s">
-        <v>161</v>
-      </c>
       <c r="G16" s="24" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H16" s="33">
         <v>24.12</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J16" s="27">
         <v>23335000</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L16" s="24"/>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="17" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A17" s="22"/>
       <c r="B17" s="13">
         <v>14</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H17" s="32">
         <v>24.12</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="J17" s="27">
         <v>9878000</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="L17" s="14"/>
       <c r="M17" s="25" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="18" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A18" s="22"/>
       <c r="B18" s="13">
         <v>15</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D18" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="I18" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="J18" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="J18" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>62</v>
-      </c>
       <c r="L18" s="14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M18" s="16"/>
     </row>
-    <row r="19" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="19" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A19" s="22"/>
       <c r="B19" s="13">
         <v>16</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="I19" s="14" t="s">
+      <c r="J19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J19" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>64</v>
-      </c>
       <c r="L19" s="14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M19" s="21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="20" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A20" s="22"/>
       <c r="B20" s="13">
         <v>17</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H20" s="14">
         <v>23.06</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J20" s="28">
         <v>11569000</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L20" s="39" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M20" s="40"/>
     </row>
-    <row r="21" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="21" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A21" s="22"/>
       <c r="B21" s="13">
         <v>18</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J21" s="28"/>
       <c r="K21" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="16"/>
     </row>
-    <row r="22" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="22" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A22" s="22"/>
       <c r="B22" s="13">
         <v>19</v>
       </c>
       <c r="C22" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="G22" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>70</v>
-      </c>
       <c r="H22" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J22" s="27"/>
       <c r="K22" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L22" s="14"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="23" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A23" s="22"/>
       <c r="B23" s="13">
         <v>20</v>
       </c>
       <c r="C23" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="G23" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>70</v>
-      </c>
       <c r="H23" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J23" s="27"/>
       <c r="K23" s="14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L23" s="14"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="24" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A24" s="22"/>
       <c r="B24" s="13">
         <v>21</v>
       </c>
       <c r="C24" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="G24" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>70</v>
-      </c>
       <c r="H24" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J24" s="27"/>
       <c r="K24" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L24" s="14"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="25" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A25" s="22"/>
       <c r="B25" s="13">
         <v>22</v>
       </c>
       <c r="C25" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="G25" s="24" t="s">
         <v>181</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>186</v>
       </c>
       <c r="H25" s="33">
         <v>25.08</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J25" s="27">
         <v>29260000</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="M25" s="25"/>
     </row>
-    <row r="26" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="26" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A26" s="22"/>
       <c r="B26" s="13">
         <v>23</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H26" s="14">
         <v>23.05</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J26" s="31" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L26" s="14"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="27" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A27" s="22"/>
       <c r="B27" s="13">
         <v>24</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H27" s="14">
         <v>24.03</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J27" s="27">
         <v>585000</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M27" s="16"/>
-      <c r="N27" s="8" t="s">
-        <v>194</v>
-      </c>
     </row>
-    <row r="28" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="28" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A28" s="22"/>
       <c r="B28" s="13">
         <v>25</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H28" s="14">
         <v>24.03</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J28" s="28">
         <v>585000</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M28" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>215</v>
+        <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="29" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A29" s="22"/>
       <c r="B29" s="13">
         <v>26</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H29" s="14">
         <v>24.03</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J29" s="28">
         <v>585000</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M29" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="30" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="30" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A30" s="22"/>
       <c r="B30" s="13">
         <v>27</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="H30" s="14">
         <v>24.03</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J30" s="28">
         <v>585000</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="M30" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="P30" s="8" t="s">
-        <v>13</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="31" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A31" s="22"/>
       <c r="B31" s="13">
         <v>28</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="H31" s="14">
         <v>24.03</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J31" s="28">
         <v>585000</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="L31" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="M31" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="M31" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="P31" s="8" t="s">
-        <v>198</v>
-      </c>
     </row>
-    <row r="32" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="32" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A32" s="22"/>
       <c r="B32" s="13">
         <v>29</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="H32" s="14">
         <v>24.03</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J32" s="28">
         <v>585000</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="M32" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>13</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="33" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A33" s="22"/>
       <c r="B33" s="13">
         <v>30</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="H33" s="14">
         <v>24.03</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J33" s="28">
         <v>585000</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M33" s="16"/>
-      <c r="P33" s="8" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="34" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="34" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A34" s="22"/>
       <c r="B34" s="13">
         <v>31</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H34" s="14">
         <v>24.03</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J34" s="27">
         <v>585000</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L34" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="M34" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="M34" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="P34" s="8" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="35" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="35" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A35" s="22"/>
       <c r="B35" s="13">
         <v>32</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="H35" s="14">
         <v>24.03</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J35" s="28">
         <v>585000</v>
       </c>
       <c r="K35" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L35" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="36" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A36" s="22"/>
       <c r="B36" s="13">
         <v>33</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="H36" s="14">
         <v>25.09</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J36" s="27">
         <v>570000</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M36" s="21"/>
-      <c r="P36" s="8" t="s">
-        <v>193</v>
-      </c>
     </row>
-    <row r="37" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="37" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A37" s="22"/>
       <c r="B37" s="13">
         <v>34</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="H37" s="14">
         <v>25.09</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J37" s="27">
         <v>570000</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M37" s="21"/>
     </row>
-    <row r="38" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="38" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A38" s="22"/>
       <c r="B38" s="13">
         <v>35</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="H38" s="14">
         <v>25.09</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J38" s="27">
         <v>570000</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M38" s="21"/>
     </row>
-    <row r="39" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="39" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A39" s="22"/>
       <c r="B39" s="13">
         <v>36</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F39" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G39" s="15" t="s">
         <v>223</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>235</v>
       </c>
       <c r="H39" s="14">
         <v>25.09</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J39" s="27">
         <v>570000</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M39" s="21"/>
     </row>
-    <row r="40" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="40" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A40" s="22"/>
       <c r="B40" s="13">
         <v>37</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="H40" s="14">
         <v>25.09</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J40" s="27">
         <v>570000</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L40" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M40" s="21"/>
     </row>
-    <row r="41" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="41" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A41" s="22"/>
       <c r="B41" s="13">
         <v>38</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H41" s="14">
         <v>25.09</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J41" s="27">
         <v>570000</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L41" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M41" s="16"/>
     </row>
-    <row r="42" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="42" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A42" s="22"/>
       <c r="B42" s="13">
         <v>39</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="H42" s="14">
         <v>25.09</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J42" s="27">
         <v>570000</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L42" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M42" s="21"/>
     </row>
-    <row r="43" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="43" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A43" s="22"/>
       <c r="B43" s="13">
         <v>40</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="H43" s="14">
         <v>25.09</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J43" s="27">
         <v>570000</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="L43" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M43" s="16"/>
     </row>
-    <row r="44" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="44" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A44" s="22"/>
       <c r="B44" s="13">
         <v>41</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H44" s="14">
         <v>25.09</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J44" s="27">
         <v>570000</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="L44" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M44" s="16"/>
     </row>
-    <row r="45" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="45" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A45" s="22"/>
       <c r="B45" s="13">
         <v>42</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="H45" s="14">
         <v>25.09</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J45" s="27">
         <v>570000</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="L45" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="M45" s="21"/>
+        <v>136</v>
+      </c>
+      <c r="M45" s="21" t="s">
+        <v>238</v>
+      </c>
     </row>
-    <row r="46" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="46" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A46" s="22"/>
       <c r="B46" s="13">
         <v>43</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J46" s="27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L46" s="14"/>
       <c r="M46" s="21"/>
     </row>
-    <row r="47" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="47" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A47" s="22"/>
       <c r="B47" s="13">
         <v>44</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H47" s="14">
         <v>23.05</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J47" s="30" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L47" s="14"/>
       <c r="M47" s="16"/>
     </row>
-    <row r="48" spans="1:16" s="8" customFormat="1" ht="50.1" customHeight="1">
+    <row r="48" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A48" s="22"/>
       <c r="B48" s="13">
         <v>45</v>
       </c>
       <c r="C48" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="G48" s="15" t="s">
         <v>25</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G48" s="15" t="s">
-        <v>28</v>
       </c>
       <c r="H48" s="14">
         <v>19.02</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J48" s="28">
         <v>11200000</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L48" s="14"/>
       <c r="M48" s="16"/>
@@ -5829,31 +5785,31 @@
         <v>46</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F49" s="24" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H49" s="33">
         <v>25.04</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J49" s="27">
         <v>9960000</v>
       </c>
       <c r="K49" s="24" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L49" s="24"/>
       <c r="M49" s="25"/>
@@ -5864,31 +5820,31 @@
         <v>47</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E50" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F50" s="18" t="s">
-        <v>33</v>
-      </c>
       <c r="G50" s="15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H50" s="14">
         <v>19.12</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J50" s="28">
         <v>11000000</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L50" s="14"/>
       <c r="M50" s="16"/>
@@ -5899,31 +5855,31 @@
         <v>48</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H51" s="14">
         <v>23.01</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J51" s="28">
         <v>708058</v>
       </c>
       <c r="K51" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L51" s="14"/>
       <c r="M51" s="16"/>
@@ -5934,27 +5890,27 @@
         <v>49</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F52" s="14"/>
       <c r="G52" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J52" s="27"/>
       <c r="K52" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L52" s="14"/>
       <c r="M52" s="16"/>
@@ -5965,27 +5921,27 @@
         <v>50</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F53" s="18"/>
       <c r="G53" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J53" s="28"/>
       <c r="K53" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L53" s="14"/>
       <c r="M53" s="16"/>
@@ -5996,7 +5952,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D54" s="36" t="s">
         <v>11</v>
@@ -6004,17 +5960,17 @@
       <c r="E54" s="34"/>
       <c r="F54" s="34"/>
       <c r="G54" s="34" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H54" s="34" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I54" s="34" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J54" s="29"/>
       <c r="K54" s="34" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L54" s="34"/>
       <c r="M54" s="38"/>

--- a/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
+++ b/99. 부가업무/4. 장비 보유 현황/EV HEATER SW_장비 관리대장.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="241">
   <si>
     <t>N0</t>
     <phoneticPr fontId="36" type="noConversion"/>
@@ -629,10 +629,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>김영준 수석</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>김진겸 사원</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -805,11 +801,6 @@
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
-    <t>대여 중
--일렉스 화재 대응-</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>x</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -988,10 +979,6 @@
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
   <si>
-    <t>Last Rev. 25.11.05</t>
-    <phoneticPr fontId="36" type="noConversion"/>
-  </si>
-  <si>
     <t>IJAZ</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
@@ -1016,11 +1003,31 @@
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
-    <t>김영준 수석</t>
+    <t>2팀 대여 중</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>조성연 전임</t>
     <phoneticPr fontId="41" type="noConversion"/>
   </si>
   <si>
-    <t>2팀 대여 중</t>
+    <t>조성연 전임</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>오세영 수석</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>(26/3/23 회수 완료)</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>조현진 전임</t>
+    <phoneticPr fontId="41" type="noConversion"/>
+  </si>
+  <si>
+    <t>Last Rev. 26.03.25</t>
     <phoneticPr fontId="36" type="noConversion"/>
   </si>
 </sst>
@@ -1371,7 +1378,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1515,6 +1522,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2968,7 +2981,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3094,6 +3107,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="46" fillId="29" borderId="3" xfId="142" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="46" fillId="29" borderId="3" xfId="142" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="418">
@@ -4073,12 +4107,12 @@
   <sheetData>
     <row r="1" spans="1:17" ht="17.25">
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="14.25" thickBot="1">
       <c r="C2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="50.1" customHeight="1">
@@ -4320,10 +4354,10 @@
         <v>96</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H9" s="14">
         <v>24.03</v>
@@ -4335,13 +4369,13 @@
         <v>585000</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M9" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
@@ -4359,10 +4393,10 @@
         <v>18</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H10" s="14">
         <v>23.06</v>
@@ -4377,7 +4411,7 @@
         <v>33</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M10" s="16"/>
     </row>
@@ -4411,10 +4445,10 @@
         <v>9591000</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M11" s="16"/>
     </row>
@@ -4424,35 +4458,35 @@
         <v>9</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D12" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="F12" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>154</v>
-      </c>
       <c r="G12" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H12" s="14">
         <v>24.12</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J12" s="27">
         <v>9878000</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="2" customFormat="1" ht="50.1" customHeight="1">
@@ -4461,35 +4495,35 @@
         <v>10</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>153</v>
-      </c>
       <c r="F13" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H13" s="14">
         <v>24.12</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J13" s="27">
         <v>9878000</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L13" s="14"/>
       <c r="M13" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4498,31 +4532,31 @@
         <v>11</v>
       </c>
       <c r="C14" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>151</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>152</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="G14" s="24" t="s">
         <v>167</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>168</v>
       </c>
       <c r="H14" s="33">
         <v>24.12</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J14" s="27">
         <v>23335000</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L14" s="24"/>
       <c r="M14" s="25"/>
@@ -4542,13 +4576,13 @@
         <v>71</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I15" s="14" t="s">
         <v>73</v>
@@ -4557,13 +4591,13 @@
         <v>9591001</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="L15" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="M15" s="21" t="s">
         <v>145</v>
-      </c>
-      <c r="M15" s="21" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4572,25 +4606,25 @@
         <v>13</v>
       </c>
       <c r="C16" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" s="24" t="s">
+      <c r="G16" s="24" t="s">
         <v>157</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>158</v>
       </c>
       <c r="H16" s="33">
         <v>24.12</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J16" s="27">
         <v>23335000</v>
@@ -4607,35 +4641,35 @@
         <v>14</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D17" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>153</v>
-      </c>
       <c r="F17" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>165</v>
       </c>
       <c r="H17" s="32">
         <v>24.12</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J17" s="27">
         <v>9878000</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="L17" s="14"/>
       <c r="M17" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -4889,34 +4923,34 @@
         <v>22</v>
       </c>
       <c r="C25" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="E25" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="E25" s="24" t="s">
-        <v>178</v>
-      </c>
       <c r="F25" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H25" s="33">
         <v>25.08</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J25" s="27">
         <v>29260000</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M25" s="25"/>
     </row>
@@ -4960,37 +4994,37 @@
       <c r="B27" s="13">
         <v>24</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="H27" s="14">
+      <c r="G27" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="H27" s="42">
         <v>24.03</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="J27" s="27">
+      <c r="J27" s="44">
         <v>585000</v>
       </c>
-      <c r="K27" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="L27" s="14" t="s">
+      <c r="K27" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="L27" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="M27" s="16"/>
+      <c r="M27" s="45"/>
     </row>
     <row r="28" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A28" s="22"/>
@@ -5010,7 +5044,7 @@
         <v>102</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H28" s="14">
         <v>24.03</v>
@@ -5022,13 +5056,13 @@
         <v>585000</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>133</v>
+        <v>237</v>
       </c>
       <c r="L28" s="14" t="s">
         <v>135</v>
       </c>
       <c r="M28" s="21" t="s">
-        <v>185</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5049,7 +5083,7 @@
         <v>103</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H29" s="14">
         <v>24.03</v>
@@ -5067,7 +5101,7 @@
         <v>137</v>
       </c>
       <c r="M29" s="21" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5088,7 +5122,7 @@
         <v>104</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H30" s="14">
         <v>24.03</v>
@@ -5103,10 +5137,10 @@
         <v>138</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M30" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5127,7 +5161,7 @@
         <v>141</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H31" s="14">
         <v>24.03</v>
@@ -5139,13 +5173,13 @@
         <v>585000</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M31" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5166,7 +5200,7 @@
         <v>127</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H32" s="14">
         <v>24.03</v>
@@ -5178,13 +5212,13 @@
         <v>585000</v>
       </c>
       <c r="K32" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="M32" s="21" t="s">
         <v>189</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="M32" s="21" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5192,37 +5226,37 @@
       <c r="B33" s="13">
         <v>30</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="G33" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="H33" s="14">
+      <c r="G33" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="H33" s="42">
         <v>24.03</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="47">
         <v>585000</v>
       </c>
-      <c r="K33" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="L33" s="14" t="s">
+      <c r="K33" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="L33" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="M33" s="16"/>
+      <c r="M33" s="45"/>
     </row>
     <row r="34" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
       <c r="A34" s="22"/>
@@ -5242,7 +5276,7 @@
         <v>140</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H34" s="14">
         <v>24.03</v>
@@ -5257,10 +5291,10 @@
         <v>126</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M34" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5281,7 +5315,7 @@
         <v>105</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H35" s="14">
         <v>24.03</v>
@@ -5299,7 +5333,7 @@
         <v>117</v>
       </c>
       <c r="M35" s="21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5317,10 +5351,10 @@
         <v>96</v>
       </c>
       <c r="F36" s="18" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H36" s="14">
         <v>25.09</v>
@@ -5332,7 +5366,7 @@
         <v>570000</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L36" s="14" t="s">
         <v>136</v>
@@ -5354,10 +5388,10 @@
         <v>96</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H37" s="14">
         <v>25.09</v>
@@ -5369,7 +5403,7 @@
         <v>570000</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L37" s="14" t="s">
         <v>136</v>
@@ -5391,10 +5425,10 @@
         <v>96</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H38" s="14">
         <v>25.09</v>
@@ -5406,7 +5440,7 @@
         <v>570000</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L38" s="14" t="s">
         <v>136</v>
@@ -5428,10 +5462,10 @@
         <v>125</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H39" s="14">
         <v>25.09</v>
@@ -5443,7 +5477,7 @@
         <v>570000</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="L39" s="14" t="s">
         <v>136</v>
@@ -5465,10 +5499,10 @@
         <v>96</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G40" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H40" s="14">
         <v>25.09</v>
@@ -5480,7 +5514,7 @@
         <v>570000</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L40" s="14" t="s">
         <v>136</v>
@@ -5502,10 +5536,10 @@
         <v>96</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G41" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H41" s="14">
         <v>25.09</v>
@@ -5517,7 +5551,7 @@
         <v>570000</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L41" s="14" t="s">
         <v>136</v>
@@ -5539,10 +5573,10 @@
         <v>96</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G42" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H42" s="14">
         <v>25.09</v>
@@ -5554,7 +5588,7 @@
         <v>570000</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L42" s="14" t="s">
         <v>136</v>
@@ -5576,10 +5610,10 @@
         <v>106</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H43" s="14">
         <v>25.09</v>
@@ -5591,7 +5625,7 @@
         <v>570000</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L43" s="14" t="s">
         <v>136</v>
@@ -5613,10 +5647,10 @@
         <v>96</v>
       </c>
       <c r="F44" s="18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H44" s="14">
         <v>25.09</v>
@@ -5628,7 +5662,7 @@
         <v>570000</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L44" s="14" t="s">
         <v>136</v>
@@ -5640,38 +5674,38 @@
       <c r="B45" s="13">
         <v>42</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="F45" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="H45" s="14">
+      <c r="F45" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="G45" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="H45" s="42">
         <v>25.09</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="J45" s="27">
+      <c r="J45" s="44">
         <v>570000</v>
       </c>
-      <c r="K45" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="L45" s="14" t="s">
+      <c r="K45" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="L45" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="M45" s="21" t="s">
-        <v>238</v>
+      <c r="M45" s="48" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="8" customFormat="1" ht="50.1" customHeight="1">
@@ -5704,7 +5738,7 @@
         <v>13</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L46" s="14"/>
       <c r="M46" s="21"/>
@@ -5785,31 +5819,31 @@
         <v>46</v>
       </c>
       <c r="C49" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="D49" s="24" t="s">
+      <c r="E49" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="F49" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="F49" s="24" t="s">
+      <c r="G49" s="24" t="s">
         <v>173</v>
-      </c>
-      <c r="G49" s="24" t="s">
-        <v>174</v>
       </c>
       <c r="H49" s="33">
         <v>25.04</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J49" s="27">
         <v>9960000</v>
       </c>
       <c r="K49" s="24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L49" s="24"/>
       <c r="M49" s="25"/>
